--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Proyectos/cursos_activos/inserta_once/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\ejercicios_excell\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54222956-CA8B-9540-87B0-F23EEB278FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D895D6-1F1E-444F-BDCC-F0864E7BBCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="740" windowWidth="38080" windowHeight="19940" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,12 @@
     <sheet name="3_Satisfaccion" sheetId="4" r:id="rId4"/>
     <sheet name="4_Probabilidad" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,12 +38,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="153">
   <si>
     <t>ID_Venta</t>
   </si>
@@ -487,6 +496,15 @@
   </si>
   <si>
     <t>Dashboard 4: Probabilidad y Frecuencias (Canales)</t>
+  </si>
+  <si>
+    <t>18 es el producto que mas se ha comprado</t>
+  </si>
+  <si>
+    <t>media y mediana no son parecidas, esto implica muchos outliners ,valores extremos en la parte alta que distorsionan la media</t>
+  </si>
+  <si>
+    <t>el tikect medio de nuestra tienda es 35</t>
   </si>
 </sst>
 </file>
@@ -574,7 +592,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -597,6 +615,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -608,16 +639,66 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -628,6 +709,735 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>histograma de precios</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{2F1EEB45-E66E-4585-B1C7-6ADAAF1B016E}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Gráfico 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA650B69-2B8E-B9E5-BEE4-338732DB0DF1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4251960" y="2225040"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-ES" sz="1100"/>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38E5041C-F245-4966-82E1-642C61AE9389}" name="Tabla1" displayName="Tabla1" ref="A1:N43" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:N43" xr:uid="{38E5041C-F245-4966-82E1-642C61AE9389}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{CD681CD3-B8DF-41F4-B1C1-97FF537BD801}" name="ID_Venta"/>
+    <tableColumn id="2" xr3:uid="{C93B0018-5E20-48BA-82D3-B1BCF9AAA83E}" name="Fecha"/>
+    <tableColumn id="3" xr3:uid="{3DCD7AF7-1476-4142-8766-C1F76B108132}" name="Producto"/>
+    <tableColumn id="4" xr3:uid="{C860820C-0280-45A9-BD77-299E45EBA132}" name="Categoría"/>
+    <tableColumn id="5" xr3:uid="{DBFE0886-E244-473C-8A50-40215C7D388D}" name="Unidades"/>
+    <tableColumn id="6" xr3:uid="{94F60386-9B1C-489F-9376-56B69932FF3D}" name="Precio_Unitario"/>
+    <tableColumn id="7" xr3:uid="{7E88048F-A511-494C-89ED-8A2EFBE4CC0D}" name="Ciudad"/>
+    <tableColumn id="8" xr3:uid="{A142C736-5DBF-40D1-9089-6B85EA08F210}" name="Canal"/>
+    <tableColumn id="9" xr3:uid="{BD47F81B-D362-477C-B900-B552C4115537}" name="Valoración"/>
+    <tableColumn id="10" xr3:uid="{02C8EB7B-74E7-4B1D-87EC-E75A25B059C4}" name="Ingresos"/>
+    <tableColumn id="11" xr3:uid="{391663B3-8D3D-45D1-A71E-985B37C2BB32}" name="Coste"/>
+    <tableColumn id="12" xr3:uid="{512DA83F-FFFA-4901-8EF0-39E7FBFCA18F}" name="Beneficio"/>
+    <tableColumn id="13" xr3:uid="{539E6CA5-D6EC-4035-A1CB-7076C5C001BB}" name="Vendedor"/>
+    <tableColumn id="14" xr3:uid="{2D4C3BD6-D8C0-4A4C-AC02-7C39FBC49E81}" name="Devolución"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -918,53 +1728,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.21875" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1008,7 +1830,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -1052,7 +1874,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1096,7 +1918,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1140,7 +1962,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -1184,7 +2006,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -1228,7 +2050,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -1272,7 +2094,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -1316,7 +2138,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1360,7 +2182,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -1404,7 +2226,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1011</v>
       </c>
@@ -1448,7 +2270,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1012</v>
       </c>
@@ -1492,7 +2314,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1013</v>
       </c>
@@ -1536,7 +2358,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1014</v>
       </c>
@@ -1580,7 +2402,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1015</v>
       </c>
@@ -1624,7 +2446,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1016</v>
       </c>
@@ -1668,7 +2490,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1017</v>
       </c>
@@ -1712,7 +2534,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1018</v>
       </c>
@@ -1756,7 +2578,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1019</v>
       </c>
@@ -1800,7 +2622,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1020</v>
       </c>
@@ -1844,7 +2666,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1021</v>
       </c>
@@ -1888,7 +2710,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1022</v>
       </c>
@@ -1932,7 +2754,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1023</v>
       </c>
@@ -1976,7 +2798,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1024</v>
       </c>
@@ -2020,7 +2842,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1025</v>
       </c>
@@ -2064,7 +2886,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1026</v>
       </c>
@@ -2108,7 +2930,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1027</v>
       </c>
@@ -2152,7 +2974,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1028</v>
       </c>
@@ -2196,7 +3018,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1029</v>
       </c>
@@ -2240,7 +3062,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1030</v>
       </c>
@@ -2284,7 +3106,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1031</v>
       </c>
@@ -2328,7 +3150,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1032</v>
       </c>
@@ -2372,7 +3194,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1033</v>
       </c>
@@ -2416,7 +3238,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1034</v>
       </c>
@@ -2460,7 +3282,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1035</v>
       </c>
@@ -2504,7 +3326,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1036</v>
       </c>
@@ -2548,7 +3370,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1037</v>
       </c>
@@ -2592,7 +3414,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1038</v>
       </c>
@@ -2636,7 +3458,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1039</v>
       </c>
@@ -2680,7 +3502,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1040</v>
       </c>
@@ -2724,7 +3546,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1041</v>
       </c>
@@ -2768,7 +3590,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1042</v>
       </c>
@@ -2814,13 +3636,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -2828,12 +3653,12 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -2847,7 +3672,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -2857,9 +3682,12 @@
       <c r="D5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E5" s="4">
+        <f>AVERAGE(B5:B46)</f>
+        <v>60.011904761904759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2869,9 +3697,12 @@
       <c r="D6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" s="4">
+        <f>MEDIAN(B5:B46)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -2881,9 +3712,12 @@
       <c r="D7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E7" s="4">
+        <f>_xlfn.MODE.SNGL(B5:B46)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -2893,9 +3727,12 @@
       <c r="D8" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E8" s="4">
+        <f>_xlfn.STDEV.S(B5:B46)</f>
+        <v>63.23692269082472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -2903,7 +3740,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -2911,7 +3748,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2922,7 +3759,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -2930,7 +3767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -2938,7 +3775,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -2946,7 +3783,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -2954,7 +3791,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -2962,7 +3799,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -2970,7 +3807,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -2978,7 +3815,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -2986,7 +3823,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -2994,7 +3831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3002,7 +3839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3010,7 +3847,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3018,7 +3855,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3026,7 +3863,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3034,7 +3871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3042,7 +3879,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3050,7 +3887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3058,7 +3895,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -3066,7 +3903,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -3074,31 +3911,40 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
       <c r="B31">
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D31" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
       <c r="B32">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
       <c r="B33">
         <v>25</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="D33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3106,7 +3952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -3114,7 +3960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -3122,7 +3968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3130,7 +3976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -3138,7 +3984,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3146,7 +3992,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3154,7 +4000,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3162,7 +4008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -3170,7 +4016,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3178,7 +4024,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3186,7 +4032,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -3194,7 +4040,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3204,13 +4050,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -3218,12 +4065,12 @@
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3240,7 +4087,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3255,7 +4102,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3270,7 +4117,7 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -3285,7 +4132,7 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3300,7 +4147,7 @@
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -3311,7 +4158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -3322,7 +4169,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3336,7 +4183,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -3347,7 +4194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -3358,7 +4205,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3369,7 +4216,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3380,7 +4227,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -3391,7 +4238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -3402,7 +4249,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -3413,7 +4260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -3424,7 +4271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -3435,7 +4282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3446,7 +4293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3457,7 +4304,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3468,7 +4315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3479,7 +4326,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3490,7 +4337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3501,7 +4348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3512,7 +4359,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3523,7 +4370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -3534,7 +4381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -3545,7 +4392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -3556,7 +4403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -3567,7 +4414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -3578,7 +4425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3589,7 +4436,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -3600,7 +4447,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -3611,7 +4458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3622,7 +4469,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -3633,7 +4480,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3644,7 +4491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3655,7 +4502,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3666,7 +4513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -3677,7 +4524,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3688,7 +4535,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3699,7 +4546,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -3710,7 +4557,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3729,7 +4576,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -3737,12 +4584,12 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3756,7 +4603,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3768,7 +4615,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3780,7 +4627,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -3792,7 +4639,7 @@
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3800,7 +4647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -3808,7 +4655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -3819,7 +4666,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3833,7 +4680,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -3845,7 +4692,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -3857,7 +4704,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3869,7 +4716,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3881,7 +4728,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -3893,7 +4740,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -3901,7 +4748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -3909,7 +4756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -3920,7 +4767,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -3928,7 +4775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3936,7 +4783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3944,7 +4791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3952,7 +4799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3960,7 +4807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3968,7 +4815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3976,7 +4823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3984,7 +4831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3992,7 +4839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4000,7 +4847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4008,7 +4855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4016,7 +4863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -4024,7 +4871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -4032,7 +4879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4040,7 +4887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -4048,7 +4895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -4056,7 +4903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -4064,7 +4911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -4072,7 +4919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -4080,7 +4927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -4088,7 +4935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4096,7 +4943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -4104,7 +4951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -4112,7 +4959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -4120,7 +4967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4128,7 +4975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -4144,25 +4991,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98BB36B-BB56-6748-8634-193EA745B178}">
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -4170,7 +5017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -4190,7 +5037,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -4201,10 +5048,10 @@
         <v>110</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F6" s="7"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -4215,10 +5062,10 @@
         <v>111</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F7" s="7"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -4229,10 +5076,10 @@
         <v>112</v>
       </c>
       <c r="E8" s="4"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F8" s="7"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -4243,10 +5090,10 @@
         <v>143</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F9" s="7"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -4254,7 +5101,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -4265,7 +5112,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -4276,7 +5123,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4287,7 +5134,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -4295,7 +5142,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -4306,7 +5153,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -4314,7 +5161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -4325,7 +5172,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -4333,7 +5180,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -4341,7 +5188,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -4349,7 +5196,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -4357,7 +5204,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -4365,7 +5212,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -4373,7 +5220,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -4381,7 +5228,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -4389,7 +5236,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -4397,7 +5244,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -4405,7 +5252,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -4413,7 +5260,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4421,7 +5268,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4429,7 +5276,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4437,7 +5284,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -4445,7 +5292,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -4453,7 +5300,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4461,7 +5308,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -4469,7 +5316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -4477,7 +5324,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -4485,7 +5332,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -4493,7 +5340,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -4501,7 +5348,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -4509,7 +5356,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4517,7 +5364,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -4525,7 +5372,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -4533,7 +5380,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -4541,7 +5388,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4549,7 +5396,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\ejercicios_excell\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D895D6-1F1E-444F-BDCC-F0864E7BBCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D6A07E-D2CB-407E-B542-970034530BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,6 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -650,6 +648,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -684,20 +696,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -709,6 +707,580 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Dispersion</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-ES" baseline="0"/>
+              <a:t>: Coste vs Beneficio</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'2_Beneficios'!$B$5:$B$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'2_Beneficios'!$C$5:$C$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9CA7-40A6-9720-BB88AB83D247}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1924039951"/>
+        <c:axId val="1924038511"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1924039951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1924038511"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1924038511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1924039951"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -787,6 +1359,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1334,6 +1946,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1417,8 +2545,49 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2499440-986D-CADD-6ECE-ED9880888E63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38E5041C-F245-4966-82E1-642C61AE9389}" name="Tabla1" displayName="Tabla1" ref="A1:N43" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38E5041C-F245-4966-82E1-642C61AE9389}" name="Tabla1" displayName="Tabla1" ref="A1:N43" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:N43" xr:uid="{38E5041C-F245-4966-82E1-642C61AE9389}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{CD681CD3-B8DF-41F4-B1C1-97FF537BD801}" name="ID_Venta"/>
@@ -4062,7 +5231,7 @@
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -4100,7 +5269,10 @@
       <c r="E5" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4">
+        <f>AVERAGE(C5:C46)</f>
+        <v>32.511904761904759</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -4115,7 +5287,10 @@
       <c r="E6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <f>_xlfn.STDEV.S(C5:C46)</f>
+        <v>20.550499399082351</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -4130,7 +5305,10 @@
       <c r="E7" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <f>MIN(C5:C46)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -4145,7 +5323,10 @@
       <c r="E8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="4">
+        <f>MAX(C5:C46)</f>
+        <v>120</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -4570,6 +5751,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\ejercicios_excell\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D6A07E-D2CB-407E-B542-970034530BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F288B8-25E8-4B0A-86EE-B6E7EA5C0CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -1283,6 +1283,381 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Distribucion de satisfaccion</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.36523600174978127"/>
+          <c:y val="5.5555555555555552E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-ES"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'3_Satisfaccion'!$D$12:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'3_Satisfaccion'!$E$12:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-151E-4B52-91C0-1D85D54FB56D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="529963200"/>
+        <c:axId val="529967040"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="529963200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="529967040"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="529967040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="529963200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -1438,6 +1813,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
   <cs:axisTitle>
@@ -2443,6 +2858,509 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2566,6 +3484,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2499440-986D-CADD-6ECE-ED9880888E63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A5AD02C-A399-E87E-9825-A83C2AF9E300}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5762,7 +6721,7 @@
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5795,7 +6754,10 @@
       <c r="D5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <f>AVERAGE(B5:B46)</f>
+        <v>4.2857142857142856</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -5807,7 +6769,10 @@
       <c r="D6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <f>MEDIAN(B5:B46)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -5819,7 +6784,10 @@
       <c r="D7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <f>_xlfn.MODE.SNGL(B5:B46)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -5872,7 +6840,10 @@
       <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4">
+        <f>COUNTIF($B$5:$B$46,D12)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -5884,7 +6855,10 @@
       <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4">
+        <f t="shared" ref="E13:E16" si="0">COUNTIF($B$5:$B$46,D13)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -5896,7 +6870,10 @@
       <c r="D14" s="3">
         <v>3</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -5908,7 +6885,10 @@
       <c r="D15" s="3">
         <v>4</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -5920,7 +6900,10 @@
       <c r="D16" s="3">
         <v>5</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -6167,6 +7150,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\ejercicios_excell\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F288B8-25E8-4B0A-86EE-B6E7EA5C0CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD39CB02-CE6F-41F1-A046-D95F486C4A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,8 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'4_Probabilidad'!$D$6:$D$8</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'4_Probabilidad'!$E$6:$E$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1658,6 +1660,483 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Probalidad / Ventas por canal</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-ES"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="95000"/>
+                      <a:alpha val="54000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4_Probabilidad'!$D$6:$D$8</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>App</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Web</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tienda</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4_Probabilidad'!$E$6:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0A6A-4185-A774-33EB42017F97}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -1853,6 +2332,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
   <cs:axisTitle>
@@ -3376,6 +3895,502 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="257">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -3525,6 +4540,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A5AD02C-A399-E87E-9825-A83C2AF9E300}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A9F12DE-9577-4A12-36F2-7482ED8DABA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7173,7 +8229,10 @@
       <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4">
+        <f>COUNTA(A5:A46)</f>
+        <v>42</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -7213,9 +8272,18 @@
       <c r="D6" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="6"/>
+      <c r="E6" s="4">
+        <f>COUNTIF($B$5:$B$46,D6)</f>
+        <v>11</v>
+      </c>
+      <c r="F6" s="7">
+        <f>E6/$E$9</f>
+        <v>0.26190476190476192</v>
+      </c>
+      <c r="G6" s="6">
+        <f>F6</f>
+        <v>0.26190476190476192</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -7227,9 +8295,18 @@
       <c r="D7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6"/>
+      <c r="E7" s="4">
+        <f t="shared" ref="E7:E8" si="0">COUNTIF($B$5:$B$46,D7)</f>
+        <v>17</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" ref="F7:F8" si="1">E7/$E$9</f>
+        <v>0.40476190476190477</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" ref="G7:G8" si="2">F7</f>
+        <v>0.40476190476190477</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -7241,9 +8318,18 @@
       <c r="D8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="6"/>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -7255,9 +8341,18 @@
       <c r="D9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6"/>
+      <c r="E9" s="4">
+        <f>SUM(E6:E8)</f>
+        <v>42</v>
+      </c>
+      <c r="F9" s="7">
+        <f>SUM(F6:F8)</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <f>F9</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -7572,5 +8667,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>